--- a/design/tables/ShopPoint.xlsx
+++ b/design/tables/ShopPoint.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopPoint" sheetId="1" r:id="R9537844445fb4c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopPoint" sheetId="1" r:id="R1072150a720142ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -366,16 +366,16 @@
         <x:v>entry</x:v>
       </x:c>
       <x:c r="C6" s="1" t="n">
-        <x:v>-35</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="D6" s="1" t="n">
-        <x:v>180</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E6" s="1" t="n">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F6" s="1" t="n">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
@@ -386,10 +386,10 @@
         <x:v>checkout</x:v>
       </x:c>
       <x:c r="C7" s="1" t="n">
-        <x:v>112</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D7" s="1" t="n">
-        <x:v>138</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E7" s="1" t="n">
         <x:v>46</x:v>
@@ -406,16 +406,16 @@
         <x:v>exit</x:v>
       </x:c>
       <x:c r="C8" s="1" t="n">
-        <x:v>-35</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="D8" s="1" t="n">
-        <x:v>180</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E8" s="1" t="n">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F8" s="1" t="n">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
@@ -426,16 +426,16 @@
         <x:v>shelf0</x:v>
       </x:c>
       <x:c r="C9" s="1" t="n">
-        <x:v>-86</x:v>
+        <x:v>-98</x:v>
       </x:c>
       <x:c r="D9" s="1" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E9" s="1" t="n">
-        <x:v>125</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F9" s="1" t="n">
-        <x:v>74</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
@@ -446,16 +446,16 @@
         <x:v>shelf1</x:v>
       </x:c>
       <x:c r="C10" s="1" t="n">
-        <x:v>-86</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D10" s="1" t="n">
-        <x:v>-5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E10" s="1" t="n">
-        <x:v>125</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F10" s="1" t="n">
-        <x:v>74</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
@@ -466,16 +466,16 @@
         <x:v>shelf2</x:v>
       </x:c>
       <x:c r="C11" s="1" t="n">
-        <x:v>70</x:v>
+        <x:v>-98</x:v>
       </x:c>
       <x:c r="D11" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>-195</x:v>
       </x:c>
       <x:c r="E11" s="1" t="n">
-        <x:v>125</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F11" s="1" t="n">
-        <x:v>74</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
@@ -486,16 +486,16 @@
         <x:v>shelf3</x:v>
       </x:c>
       <x:c r="C12" s="1" t="n">
-        <x:v>70</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D12" s="1" t="n">
-        <x:v>-100</x:v>
+        <x:v>-195</x:v>
       </x:c>
       <x:c r="E12" s="1" t="n">
-        <x:v>125</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F12" s="1" t="n">
-        <x:v>74</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
@@ -506,16 +506,16 @@
         <x:v>worker0</x:v>
       </x:c>
       <x:c r="C13" s="1" t="n">
-        <x:v>144</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D13" s="1" t="n">
-        <x:v>150</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E13" s="1" t="n">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F13" s="1" t="n">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
@@ -526,16 +526,16 @@
         <x:v>worker1</x:v>
       </x:c>
       <x:c r="C14" s="1" t="n">
-        <x:v>-148</x:v>
+        <x:v>-157</x:v>
       </x:c>
       <x:c r="D14" s="1" t="n">
-        <x:v>80</x:v>
+        <x:v>-35</x:v>
       </x:c>
       <x:c r="E14" s="1" t="n">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F14" s="1" t="n">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
@@ -546,16 +546,16 @@
         <x:v>worker2</x:v>
       </x:c>
       <x:c r="C15" s="1" t="n">
-        <x:v>-145</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D15" s="1" t="n">
-        <x:v>-26</x:v>
+        <x:v>-35</x:v>
       </x:c>
       <x:c r="E15" s="1" t="n">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F15" s="1" t="n">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
@@ -566,16 +566,16 @@
         <x:v>worker3</x:v>
       </x:c>
       <x:c r="C16" s="1" t="n">
-        <x:v>142</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D16" s="1" t="n">
-        <x:v>-95</x:v>
+        <x:v>-230</x:v>
       </x:c>
       <x:c r="E16" s="1" t="n">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F16" s="1" t="n">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
@@ -586,10 +586,10 @@
         <x:v>queue</x:v>
       </x:c>
       <x:c r="C17" s="1" t="n">
-        <x:v>150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="1" t="n">
-        <x:v>75</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E17" s="1" t="n">
         <x:v>46</x:v>
@@ -609,13 +609,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="1" t="n">
-        <x:v>-35</x:v>
+        <x:v>-48</x:v>
       </x:c>
       <x:c r="E18" s="1" t="n">
-        <x:v>46</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="1" t="n">
-        <x:v>46</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
@@ -626,10 +626,10 @@
         <x:v>browseOffset</x:v>
       </x:c>
       <x:c r="C19" s="1" t="n">
-        <x:v>-15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="1" t="n">
-        <x:v>-45</x:v>
+        <x:v>-92</x:v>
       </x:c>
       <x:c r="E19" s="1" t="n">
         <x:v>1</x:v>
@@ -646,15 +646,55 @@
         <x:v>restockOffset</x:v>
       </x:c>
       <x:c r="C20" s="1" t="n">
-        <x:v>-55</x:v>
+        <x:v>-67</x:v>
       </x:c>
       <x:c r="D20" s="1" t="n">
+        <x:v>-92</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>entryLane</x:v>
+      </x:c>
+      <x:c r="C21" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="n">
+      <x:c r="D21" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="E21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>checkoutLane</x:v>
+      </x:c>
+      <x:c r="C22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/design/tables/ShopPoint.xlsx
+++ b/design/tables/ShopPoint.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopPoint" sheetId="1" r:id="R1072150a720142ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopPoint" sheetId="1" r:id="Rd32f5a4c0dfd4867"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -366,10 +366,10 @@
         <x:v>entry</x:v>
       </x:c>
       <x:c r="C6" s="1" t="n">
-        <x:v>-150</x:v>
+        <x:v>-120</x:v>
       </x:c>
       <x:c r="D6" s="1" t="n">
-        <x:v>152</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E6" s="1" t="n">
         <x:v>46</x:v>
@@ -406,10 +406,10 @@
         <x:v>exit</x:v>
       </x:c>
       <x:c r="C8" s="1" t="n">
-        <x:v>-150</x:v>
+        <x:v>-120</x:v>
       </x:c>
       <x:c r="D8" s="1" t="n">
-        <x:v>152</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E8" s="1" t="n">
         <x:v>46</x:v>
@@ -646,10 +646,10 @@
         <x:v>restockOffset</x:v>
       </x:c>
       <x:c r="C20" s="1" t="n">
-        <x:v>-67</x:v>
+        <x:v>-70</x:v>
       </x:c>
       <x:c r="D20" s="1" t="n">
-        <x:v>-92</x:v>
+        <x:v>-48</x:v>
       </x:c>
       <x:c r="E20" s="1" t="n">
         <x:v>1</x:v>
@@ -669,7 +669,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" t="n">
-        <x:v>152</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E21" t="n">
         <x:v>1</x:v>
@@ -695,6 +695,66 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>stockroom</x:v>
+      </x:c>
+      <x:c r="C23" t="n">
+        <x:v>-167</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="E23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>checkoutEffect</x:v>
+      </x:c>
+      <x:c r="C24" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="E24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>walletEffect</x:v>
+      </x:c>
+      <x:c r="C25" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="E25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/design/tables/ShopPoint.xlsx
+++ b/design/tables/ShopPoint.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopPoint" sheetId="1" r:id="Rd32f5a4c0dfd4867"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopPoint" sheetId="1" r:id="Rc143ba1cad434b36"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -331,12 +331,24 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="1" t="str"/>
-      <x:c r="B4" s="1" t="str"/>
-      <x:c r="C4" s="1" t="str"/>
-      <x:c r="D4" s="1" t="str"/>
-      <x:c r="E4" s="1" t="str"/>
-      <x:c r="F4" s="1" t="str"/>
+      <x:c r="A4" s="1" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="str">
+        <x:v>key</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="str">
+        <x:v>x</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="str">
+        <x:v>y</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="str">
+        <x:v>width</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="str">
+        <x:v>height</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="3" t="str">
@@ -369,7 +381,7 @@
         <x:v>-120</x:v>
       </x:c>
       <x:c r="D6" s="1" t="n">
-        <x:v>143</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E6" s="1" t="n">
         <x:v>46</x:v>
@@ -389,7 +401,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="D7" s="1" t="n">
-        <x:v>111</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E7" s="1" t="n">
         <x:v>46</x:v>
@@ -409,7 +421,7 @@
         <x:v>-120</x:v>
       </x:c>
       <x:c r="D8" s="1" t="n">
-        <x:v>143</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E8" s="1" t="n">
         <x:v>46</x:v>
@@ -506,10 +518,10 @@
         <x:v>worker0</x:v>
       </x:c>
       <x:c r="C13" s="1" t="n">
-        <x:v>120</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D13" s="1" t="n">
-        <x:v>172</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="E13" s="1" t="n">
         <x:v>48</x:v>
@@ -669,7 +681,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" t="n">
-        <x:v>143</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E21" t="n">
         <x:v>1</x:v>
@@ -706,16 +718,16 @@
         <x:v>stockroom</x:v>
       </x:c>
       <x:c r="C23" t="n">
-        <x:v>-167</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="D23" t="n">
-        <x:v>143</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E23" t="n">
-        <x:v>1</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F23" t="n">
-        <x:v>1</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -756,6 +768,246 @@
       </x:c>
       <x:c r="F25" t="n">
         <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>shelf4</x:v>
+      </x:c>
+      <x:c r="C26" t="n">
+        <x:v>-98</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>-390</x:v>
+      </x:c>
+      <x:c r="E26" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F26" t="n">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>worker4</x:v>
+      </x:c>
+      <x:c r="C27" t="n">
+        <x:v>-150</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>-320</x:v>
+      </x:c>
+      <x:c r="E27" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F27" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>shelf5</x:v>
+      </x:c>
+      <x:c r="C28" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D28" t="n">
+        <x:v>-390</x:v>
+      </x:c>
+      <x:c r="E28" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F28" t="n">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>worker5</x:v>
+      </x:c>
+      <x:c r="C29" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D29" t="n">
+        <x:v>-320</x:v>
+      </x:c>
+      <x:c r="E29" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F29" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>shelf6</x:v>
+      </x:c>
+      <x:c r="C30" t="n">
+        <x:v>-98</x:v>
+      </x:c>
+      <x:c r="D30" t="n">
+        <x:v>-585</x:v>
+      </x:c>
+      <x:c r="E30" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F30" t="n">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>worker6</x:v>
+      </x:c>
+      <x:c r="C31" t="n">
+        <x:v>-150</x:v>
+      </x:c>
+      <x:c r="D31" t="n">
+        <x:v>-515</x:v>
+      </x:c>
+      <x:c r="E31" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F31" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>shelf7</x:v>
+      </x:c>
+      <x:c r="C32" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D32" t="n">
+        <x:v>-585</x:v>
+      </x:c>
+      <x:c r="E32" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F32" t="n">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>worker7</x:v>
+      </x:c>
+      <x:c r="C33" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D33" t="n">
+        <x:v>-515</x:v>
+      </x:c>
+      <x:c r="E33" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F33" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>checkout2</x:v>
+      </x:c>
+      <x:c r="C34" t="n">
+        <x:v>-65</x:v>
+      </x:c>
+      <x:c r="D34" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="E34" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F34" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>pack</x:v>
+      </x:c>
+      <x:c r="C35" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D35" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E35" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F35" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>welcome</x:v>
+      </x:c>
+      <x:c r="C36" t="n">
+        <x:v>-95</x:v>
+      </x:c>
+      <x:c r="D36" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="E36" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F36" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>cashier2</x:v>
+      </x:c>
+      <x:c r="C37" t="n">
+        <x:v>-105</x:v>
+      </x:c>
+      <x:c r="D37" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="E37" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F37" t="n">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/ShopPoint.xlsx
+++ b/design/tables/ShopPoint.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopPoint" sheetId="1" r:id="Rc143ba1cad434b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopPoint" sheetId="1" r:id="R910305cadf364a37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -378,10 +378,10 @@
         <x:v>entry</x:v>
       </x:c>
       <x:c r="C6" s="1" t="n">
-        <x:v>-120</x:v>
+        <x:v>-145</x:v>
       </x:c>
       <x:c r="D6" s="1" t="n">
-        <x:v>204</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="E6" s="1" t="n">
         <x:v>46</x:v>
@@ -398,10 +398,10 @@
         <x:v>checkout</x:v>
       </x:c>
       <x:c r="C7" s="1" t="n">
-        <x:v>65</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D7" s="1" t="n">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E7" s="1" t="n">
         <x:v>46</x:v>
@@ -418,10 +418,10 @@
         <x:v>exit</x:v>
       </x:c>
       <x:c r="C8" s="1" t="n">
-        <x:v>-120</x:v>
+        <x:v>-145</x:v>
       </x:c>
       <x:c r="D8" s="1" t="n">
-        <x:v>204</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="E8" s="1" t="n">
         <x:v>46</x:v>
@@ -438,16 +438,16 @@
         <x:v>shelf0</x:v>
       </x:c>
       <x:c r="C9" s="1" t="n">
-        <x:v>-98</x:v>
+        <x:v>-103</x:v>
       </x:c>
       <x:c r="D9" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="E9" s="1" t="n">
-        <x:v>144</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F9" s="1" t="n">
-        <x:v>170</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
@@ -458,16 +458,16 @@
         <x:v>shelf1</x:v>
       </x:c>
       <x:c r="C10" s="1" t="n">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D10" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="E10" s="1" t="n">
-        <x:v>144</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F10" s="1" t="n">
-        <x:v>170</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
@@ -478,16 +478,16 @@
         <x:v>shelf2</x:v>
       </x:c>
       <x:c r="C11" s="1" t="n">
-        <x:v>-98</x:v>
+        <x:v>-103</x:v>
       </x:c>
       <x:c r="D11" s="1" t="n">
-        <x:v>-195</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="E11" s="1" t="n">
-        <x:v>144</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F11" s="1" t="n">
-        <x:v>170</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
@@ -498,16 +498,16 @@
         <x:v>shelf3</x:v>
       </x:c>
       <x:c r="C12" s="1" t="n">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D12" s="1" t="n">
-        <x:v>-195</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="E12" s="1" t="n">
-        <x:v>144</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F12" s="1" t="n">
-        <x:v>170</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
@@ -518,10 +518,10 @@
         <x:v>worker0</x:v>
       </x:c>
       <x:c r="C13" s="1" t="n">
-        <x:v>105</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D13" s="1" t="n">
-        <x:v>165</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E13" s="1" t="n">
         <x:v>48</x:v>
@@ -598,10 +598,10 @@
         <x:v>queue</x:v>
       </x:c>
       <x:c r="C17" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D17" s="1" t="n">
-        <x:v>61</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E17" s="1" t="n">
         <x:v>46</x:v>
@@ -621,7 +621,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="1" t="n">
-        <x:v>-48</x:v>
+        <x:v>-34</x:v>
       </x:c>
       <x:c r="E18" s="1" t="n">
         <x:v>1</x:v>
@@ -641,7 +641,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="1" t="n">
-        <x:v>-92</x:v>
+        <x:v>-72</x:v>
       </x:c>
       <x:c r="E19" s="1" t="n">
         <x:v>1</x:v>
@@ -658,10 +658,10 @@
         <x:v>restockOffset</x:v>
       </x:c>
       <x:c r="C20" s="1" t="n">
-        <x:v>-70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D20" s="1" t="n">
-        <x:v>-48</x:v>
+        <x:v>-45</x:v>
       </x:c>
       <x:c r="E20" s="1" t="n">
         <x:v>1</x:v>
@@ -681,7 +681,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" t="n">
-        <x:v>204</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="E21" t="n">
         <x:v>1</x:v>
@@ -701,7 +701,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" t="n">
-        <x:v>111</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E22" t="n">
         <x:v>1</x:v>
@@ -718,10 +718,10 @@
         <x:v>stockroom</x:v>
       </x:c>
       <x:c r="C23" t="n">
-        <x:v>-150</x:v>
+        <x:v>-148</x:v>
       </x:c>
       <x:c r="D23" t="n">
-        <x:v>184</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E23" t="n">
         <x:v>44</x:v>
@@ -738,10 +738,10 @@
         <x:v>checkoutEffect</x:v>
       </x:c>
       <x:c r="C24" t="n">
-        <x:v>85</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D24" t="n">
-        <x:v>156</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E24" t="n">
         <x:v>1</x:v>
@@ -758,10 +758,10 @@
         <x:v>walletEffect</x:v>
       </x:c>
       <x:c r="C25" t="n">
-        <x:v>70</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D25" t="n">
-        <x:v>310</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E25" t="n">
         <x:v>1</x:v>
@@ -778,16 +778,16 @@
         <x:v>shelf4</x:v>
       </x:c>
       <x:c r="C26" t="n">
-        <x:v>-98</x:v>
+        <x:v>-103</x:v>
       </x:c>
       <x:c r="D26" t="n">
-        <x:v>-390</x:v>
+        <x:v>-380</x:v>
       </x:c>
       <x:c r="E26" t="n">
-        <x:v>150</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F26" t="n">
-        <x:v>113</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -818,16 +818,16 @@
         <x:v>shelf5</x:v>
       </x:c>
       <x:c r="C28" t="n">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D28" t="n">
-        <x:v>-390</x:v>
+        <x:v>-380</x:v>
       </x:c>
       <x:c r="E28" t="n">
-        <x:v>150</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F28" t="n">
-        <x:v>113</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -858,16 +858,16 @@
         <x:v>shelf6</x:v>
       </x:c>
       <x:c r="C30" t="n">
-        <x:v>-98</x:v>
+        <x:v>-103</x:v>
       </x:c>
       <x:c r="D30" t="n">
-        <x:v>-585</x:v>
+        <x:v>-560</x:v>
       </x:c>
       <x:c r="E30" t="n">
-        <x:v>150</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F30" t="n">
-        <x:v>113</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -898,16 +898,16 @@
         <x:v>shelf7</x:v>
       </x:c>
       <x:c r="C32" t="n">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D32" t="n">
-        <x:v>-585</x:v>
+        <x:v>-560</x:v>
       </x:c>
       <x:c r="E32" t="n">
-        <x:v>150</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F32" t="n">
-        <x:v>113</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -938,10 +938,10 @@
         <x:v>checkout2</x:v>
       </x:c>
       <x:c r="C34" t="n">
-        <x:v>-65</x:v>
+        <x:v>-75</x:v>
       </x:c>
       <x:c r="D34" t="n">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E34" t="n">
         <x:v>44</x:v>
@@ -958,10 +958,10 @@
         <x:v>pack</x:v>
       </x:c>
       <x:c r="C35" t="n">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D35" t="n">
-        <x:v>105</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E35" t="n">
         <x:v>44</x:v>
@@ -978,10 +978,10 @@
         <x:v>welcome</x:v>
       </x:c>
       <x:c r="C36" t="n">
-        <x:v>-95</x:v>
+        <x:v>-118</x:v>
       </x:c>
       <x:c r="D36" t="n">
-        <x:v>174</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E36" t="n">
         <x:v>44</x:v>
@@ -998,10 +998,10 @@
         <x:v>cashier2</x:v>
       </x:c>
       <x:c r="C37" t="n">
-        <x:v>-105</x:v>
+        <x:v>-116</x:v>
       </x:c>
       <x:c r="D37" t="n">
-        <x:v>165</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E37" t="n">
         <x:v>48</x:v>

--- a/design/tables/ShopPoint.xlsx
+++ b/design/tables/ShopPoint.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopPoint" sheetId="1" r:id="R910305cadf364a37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopPoint" sheetId="1" r:id="Rc74da6a923ea4d0e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -378,10 +378,10 @@
         <x:v>entry</x:v>
       </x:c>
       <x:c r="C6" s="1" t="n">
-        <x:v>-145</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="1" t="n">
-        <x:v>228</x:v>
+        <x:v>-340</x:v>
       </x:c>
       <x:c r="E6" s="1" t="n">
         <x:v>46</x:v>
@@ -418,10 +418,10 @@
         <x:v>exit</x:v>
       </x:c>
       <x:c r="C8" s="1" t="n">
-        <x:v>-145</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="1" t="n">
-        <x:v>228</x:v>
+        <x:v>-340</x:v>
       </x:c>
       <x:c r="E8" s="1" t="n">
         <x:v>46</x:v>
@@ -681,7 +681,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" t="n">
-        <x:v>228</x:v>
+        <x:v>-260</x:v>
       </x:c>
       <x:c r="E21" t="n">
         <x:v>1</x:v>

--- a/design/tables/ShopPoint.xlsx
+++ b/design/tables/ShopPoint.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopPoint" sheetId="1" r:id="Rc74da6a923ea4d0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopPoint" sheetId="1" r:id="Ra07711b768db47b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -438,7 +438,7 @@
         <x:v>shelf0</x:v>
       </x:c>
       <x:c r="C9" s="1" t="n">
-        <x:v>-103</x:v>
+        <x:v>-124</x:v>
       </x:c>
       <x:c r="D9" s="1" t="n">
         <x:v>-20</x:v>
@@ -458,7 +458,7 @@
         <x:v>shelf1</x:v>
       </x:c>
       <x:c r="C10" s="1" t="n">
-        <x:v>103</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D10" s="1" t="n">
         <x:v>-20</x:v>
@@ -478,7 +478,7 @@
         <x:v>shelf2</x:v>
       </x:c>
       <x:c r="C11" s="1" t="n">
-        <x:v>-103</x:v>
+        <x:v>-124</x:v>
       </x:c>
       <x:c r="D11" s="1" t="n">
         <x:v>-200</x:v>
@@ -498,7 +498,7 @@
         <x:v>shelf3</x:v>
       </x:c>
       <x:c r="C12" s="1" t="n">
-        <x:v>103</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D12" s="1" t="n">
         <x:v>-200</x:v>
@@ -598,10 +598,10 @@
         <x:v>queue</x:v>
       </x:c>
       <x:c r="C17" s="1" t="n">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="1" t="n">
-        <x:v>118</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E17" s="1" t="n">
         <x:v>46</x:v>
@@ -621,7 +621,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="1" t="n">
-        <x:v>-34</x:v>
+        <x:v>-52</x:v>
       </x:c>
       <x:c r="E18" s="1" t="n">
         <x:v>1</x:v>
@@ -658,7 +658,7 @@
         <x:v>restockOffset</x:v>
       </x:c>
       <x:c r="C20" s="1" t="n">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D20" s="1" t="n">
         <x:v>-45</x:v>
@@ -778,7 +778,7 @@
         <x:v>shelf4</x:v>
       </x:c>
       <x:c r="C26" t="n">
-        <x:v>-103</x:v>
+        <x:v>-124</x:v>
       </x:c>
       <x:c r="D26" t="n">
         <x:v>-380</x:v>
@@ -818,7 +818,7 @@
         <x:v>shelf5</x:v>
       </x:c>
       <x:c r="C28" t="n">
-        <x:v>103</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D28" t="n">
         <x:v>-380</x:v>
@@ -858,7 +858,7 @@
         <x:v>shelf6</x:v>
       </x:c>
       <x:c r="C30" t="n">
-        <x:v>-103</x:v>
+        <x:v>-124</x:v>
       </x:c>
       <x:c r="D30" t="n">
         <x:v>-560</x:v>
@@ -898,7 +898,7 @@
         <x:v>shelf7</x:v>
       </x:c>
       <x:c r="C32" t="n">
-        <x:v>103</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D32" t="n">
         <x:v>-560</x:v>
@@ -1008,6 +1008,66 @@
       </x:c>
       <x:c r="F37" t="n">
         <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>walkLeft</x:v>
+      </x:c>
+      <x:c r="C38" t="n">
+        <x:v>-44</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>-260</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>walkRight</x:v>
+      </x:c>
+      <x:c r="C39" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>-260</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>customerClearance</x:v>
+      </x:c>
+      <x:c r="C40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>46</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
